--- a/datasets/Data_training/AQI_daily_2024_Okhla_Phase-2_Delhi_DPCC_2024.xlsx
+++ b/datasets/Data_training/AQI_daily_2024_Okhla_Phase-2_Delhi_DPCC_2024.xlsx
@@ -1,24 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Navyaa\college\ecoaware\datasets\Data_training\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC3227B7-2915-4473-8187-9FC2611A1B3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
-    <t>Day</t>
-  </si>
-  <si>
     <t>January</t>
   </si>
   <si>
@@ -80,13 +83,16 @@
   </si>
   <si>
     <t>% of Availability</t>
+  </si>
+  <si>
+    <t>Date</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -149,13 +155,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -193,7 +207,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -227,6 +241,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -261,9 +276,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -436,52 +452,52 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M42"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -522,7 +538,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -563,7 +579,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -604,7 +620,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -645,7 +661,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -686,7 +702,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -727,7 +743,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -768,7 +784,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -809,7 +825,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -850,7 +866,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -891,7 +907,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -932,7 +948,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -970,7 +986,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1011,7 +1027,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1049,7 +1065,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1090,7 +1106,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1131,7 +1147,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1172,7 +1188,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1213,7 +1229,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1254,7 +1270,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1295,7 +1311,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1336,7 +1352,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1377,7 +1393,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1418,7 +1434,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1459,7 +1475,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1497,7 +1513,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1538,7 +1554,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1576,7 +1592,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1617,7 +1633,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1658,7 +1674,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1696,7 +1712,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1722,14 +1738,14 @@
         <v>327</v>
       </c>
     </row>
-    <row r="33" spans="1:13">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13">
-      <c r="A34" t="s">
-        <v>14</v>
       </c>
       <c r="H34">
         <v>2</v>
@@ -1741,9 +1757,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:13">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G35">
         <v>3</v>
@@ -1758,9 +1774,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="1:13">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C36">
         <v>13</v>
@@ -1793,9 +1809,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:13">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C37">
         <v>12</v>
@@ -1825,9 +1841,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:13">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B38">
         <v>24</v>
@@ -1848,9 +1864,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:13">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B39">
         <v>6</v>
@@ -1862,7 +1878,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:13">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B40">
         <v>1</v>
       </c>
@@ -1876,14 +1892,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:13">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13">
-      <c r="A42" t="s">
-        <v>21</v>
       </c>
       <c r="B42">
         <v>96</v>
